--- a/results/backtest_results.xlsx
+++ b/results/backtest_results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Backtest Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -68,7 +71,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -76,13 +79,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -491,57 +503,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Quality Score</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Quality Grade</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Fresh Reversal Entry Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Fresh Reversal Entry Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Re-Accumulation Date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Retest Date</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>BOS1 Breakout Date</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>PRE_BOS2_READY (Fresh-Entry) Date</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>SL Level</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Target Price</t>
         </is>
@@ -556,7 +568,7 @@
       <c r="B2" t="n">
         <v>68.59999999999999</v>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -600,7 +612,7 @@
       <c r="B3" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -644,7 +656,7 @@
       <c r="B4" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -693,7 +705,7 @@
       <c r="B5" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -737,7 +749,7 @@
       <c r="B6" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -786,7 +798,7 @@
       <c r="B7" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -835,7 +847,7 @@
       <c r="B8" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -884,7 +896,7 @@
       <c r="B9" t="n">
         <v>87</v>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -928,7 +940,7 @@
       <c r="B10" t="n">
         <v>80.7</v>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -972,7 +984,7 @@
       <c r="B11" t="n">
         <v>81</v>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1021,7 +1033,7 @@
       <c r="B12" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1065,7 +1077,7 @@
       <c r="B13" t="n">
         <v>71.8</v>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1114,7 +1126,7 @@
       <c r="B14" t="n">
         <v>69.2</v>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1158,7 +1170,7 @@
       <c r="B15" t="n">
         <v>67.8</v>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1207,7 +1219,7 @@
       <c r="B16" t="n">
         <v>72.2</v>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1256,7 +1268,7 @@
       <c r="B17" t="n">
         <v>71.8</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1300,7 +1312,7 @@
       <c r="B18" t="n">
         <v>71.8</v>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1349,7 +1361,7 @@
       <c r="B19" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1398,7 +1410,7 @@
       <c r="B20" t="n">
         <v>71.8</v>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1447,7 +1459,7 @@
       <c r="B21" t="n">
         <v>76.7</v>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1491,7 +1503,7 @@
       <c r="B22" t="n">
         <v>76.2</v>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1535,7 +1547,7 @@
       <c r="B23" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1584,7 +1596,7 @@
       <c r="B24" t="n">
         <v>50.3</v>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -1628,7 +1640,7 @@
       <c r="B25" t="n">
         <v>72.2</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1677,7 +1689,7 @@
       <c r="B26" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1726,7 +1738,7 @@
       <c r="B27" t="n">
         <v>91</v>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1770,7 +1782,7 @@
       <c r="B28" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1819,7 +1831,7 @@
       <c r="B29" t="n">
         <v>59.8</v>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -1863,7 +1875,7 @@
       <c r="B30" t="n">
         <v>72.2</v>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -1907,7 +1919,7 @@
       <c r="B31" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -1956,7 +1968,7 @@
       <c r="B32" t="n">
         <v>65.09999999999999</v>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2005,7 +2017,7 @@
       <c r="B33" t="n">
         <v>73.2</v>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2054,7 +2066,7 @@
       <c r="B34" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2103,7 +2115,7 @@
       <c r="B35" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2152,7 +2164,7 @@
       <c r="B36" t="n">
         <v>71.8</v>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2196,7 +2208,7 @@
       <c r="B37" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2245,7 +2257,7 @@
       <c r="B38" t="n">
         <v>76.7</v>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2294,7 +2306,7 @@
       <c r="B39" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2343,7 +2355,7 @@
       <c r="B40" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2392,7 +2404,7 @@
       <c r="B41" t="n">
         <v>67.8</v>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2436,7 +2448,7 @@
       <c r="B42" t="n">
         <v>80.7</v>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2480,7 +2492,7 @@
       <c r="B43" t="n">
         <v>73.59999999999999</v>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2524,7 +2536,7 @@
       <c r="B44" t="n">
         <v>67.8</v>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2568,7 +2580,7 @@
       <c r="B45" t="n">
         <v>54.8</v>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -2612,7 +2624,7 @@
       <c r="B46" t="n">
         <v>63.8</v>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -2661,7 +2673,7 @@
       <c r="B47" t="n">
         <v>67.8</v>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2710,7 +2722,7 @@
       <c r="B48" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2759,7 +2771,7 @@
       <c r="B49" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2808,7 +2820,7 @@
       <c r="B50" t="n">
         <v>80.7</v>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2852,7 +2864,7 @@
       <c r="B51" t="n">
         <v>77.7</v>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -2901,7 +2913,7 @@
       <c r="B52" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -2950,7 +2962,7 @@
       <c r="B53" t="n">
         <v>63.2</v>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -2999,7 +3011,7 @@
       <c r="B54" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3048,7 +3060,7 @@
       <c r="B55" t="n">
         <v>71.8</v>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -3092,7 +3104,7 @@
       <c r="B56" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -3141,7 +3153,7 @@
       <c r="B57" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3190,7 +3202,7 @@
       <c r="B58" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3239,7 +3251,7 @@
       <c r="B59" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3288,7 +3300,7 @@
       <c r="B60" t="n">
         <v>72.8</v>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -3332,7 +3344,7 @@
       <c r="B61" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3381,7 +3393,7 @@
       <c r="B62" t="n">
         <v>80.7</v>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3425,7 +3437,7 @@
       <c r="B63" t="n">
         <v>53.3</v>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -3474,7 +3486,7 @@
       <c r="B64" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3523,7 +3535,7 @@
       <c r="B65" t="n">
         <v>58.8</v>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -3572,7 +3584,7 @@
       <c r="B66" t="n">
         <v>63.2</v>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -3616,7 +3628,7 @@
       <c r="B67" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3660,7 +3672,7 @@
       <c r="B68" t="n">
         <v>77.7</v>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -3709,7 +3721,7 @@
       <c r="B69" t="n">
         <v>80.7</v>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3753,7 +3765,7 @@
       <c r="B70" t="n">
         <v>68.2</v>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -3802,7 +3814,7 @@
       <c r="B71" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3851,7 +3863,7 @@
       <c r="B72" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -3895,7 +3907,7 @@
       <c r="B73" t="n">
         <v>72.2</v>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -3944,7 +3956,7 @@
       <c r="B74" t="n">
         <v>73.7</v>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -3993,7 +4005,7 @@
       <c r="B75" t="n">
         <v>60.2</v>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -4042,7 +4054,7 @@
       <c r="B76" t="n">
         <v>80.7</v>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4091,7 +4103,7 @@
       <c r="B77" t="n">
         <v>80.7</v>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4135,7 +4147,7 @@
       <c r="B78" t="n">
         <v>72.2</v>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -4184,7 +4196,7 @@
       <c r="B79" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4233,7 +4245,7 @@
       <c r="B80" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4282,7 +4294,7 @@
       <c r="B81" t="n">
         <v>95</v>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4331,7 +4343,7 @@
       <c r="B82" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4380,7 +4392,7 @@
       <c r="B83" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4429,7 +4441,7 @@
       <c r="B84" t="n">
         <v>76.7</v>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -4473,7 +4485,7 @@
       <c r="B85" t="n">
         <v>56.2</v>
       </c>
-      <c r="C85" s="4" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -4522,7 +4534,7 @@
       <c r="B86" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4571,7 +4583,7 @@
       <c r="B87" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4620,7 +4632,7 @@
       <c r="B88" t="n">
         <v>71.8</v>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -4669,7 +4681,7 @@
       <c r="B89" t="n">
         <v>91</v>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4718,7 +4730,7 @@
       <c r="B90" t="n">
         <v>73.2</v>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -4767,7 +4779,7 @@
       <c r="B91" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4816,7 +4828,7 @@
       <c r="B92" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4865,7 +4877,7 @@
       <c r="B93" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -4914,7 +4926,7 @@
       <c r="B94" t="n">
         <v>68.8</v>
       </c>
-      <c r="C94" s="2" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -4963,7 +4975,7 @@
       <c r="B95" t="n">
         <v>71.8</v>
       </c>
-      <c r="C95" s="2" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -5012,7 +5024,7 @@
       <c r="B96" t="n">
         <v>50.3</v>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -5056,7 +5068,7 @@
       <c r="B97" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5100,7 +5112,7 @@
       <c r="B98" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5144,7 +5156,7 @@
       <c r="B99" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -5193,7 +5205,7 @@
       <c r="B100" t="n">
         <v>77.7</v>
       </c>
-      <c r="C100" s="2" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -5242,7 +5254,7 @@
       <c r="B101" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5291,7 +5303,7 @@
       <c r="B102" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5340,7 +5352,7 @@
       <c r="B103" t="n">
         <v>88</v>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5389,7 +5401,7 @@
       <c r="B104" t="n">
         <v>94</v>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5438,7 +5450,7 @@
       <c r="B105" t="n">
         <v>95</v>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5487,7 +5499,7 @@
       <c r="B106" t="n">
         <v>59.8</v>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C106" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -5536,7 +5548,7 @@
       <c r="B107" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5580,7 +5592,7 @@
       <c r="B108" t="n">
         <v>72.2</v>
       </c>
-      <c r="C108" s="2" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -5624,7 +5636,7 @@
       <c r="B109" t="n">
         <v>80.7</v>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5668,7 +5680,7 @@
       <c r="B110" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5717,7 +5729,7 @@
       <c r="B111" t="n">
         <v>71.7</v>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -5761,7 +5773,7 @@
       <c r="B112" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5810,7 +5822,7 @@
       <c r="B113" t="n">
         <v>88</v>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5859,7 +5871,7 @@
       <c r="B114" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="C114" s="2" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -5908,7 +5920,7 @@
       <c r="B115" t="n">
         <v>87</v>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -5957,7 +5969,7 @@
       <c r="B116" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6006,7 +6018,7 @@
       <c r="B117" t="n">
         <v>76.7</v>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -6050,7 +6062,7 @@
       <c r="B118" t="n">
         <v>80.7</v>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6094,7 +6106,7 @@
       <c r="B119" t="n">
         <v>76.7</v>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -6143,7 +6155,7 @@
       <c r="B120" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6192,7 +6204,7 @@
       <c r="B121" t="n">
         <v>82</v>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6241,7 +6253,7 @@
       <c r="B122" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6290,7 +6302,7 @@
       <c r="B123" t="n">
         <v>71.8</v>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -6334,7 +6346,7 @@
       <c r="B124" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6383,7 +6395,7 @@
       <c r="B125" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6432,7 +6444,7 @@
       <c r="B126" t="n">
         <v>74</v>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -6476,7 +6488,7 @@
       <c r="B127" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -6520,7 +6532,7 @@
       <c r="B128" t="n">
         <v>68.8</v>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -6569,7 +6581,7 @@
       <c r="B129" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6618,7 +6630,7 @@
       <c r="B130" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6667,7 +6679,7 @@
       <c r="B131" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6716,7 +6728,7 @@
       <c r="B132" t="n">
         <v>77.7</v>
       </c>
-      <c r="C132" s="2" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -6765,7 +6777,7 @@
       <c r="B133" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6814,7 +6826,7 @@
       <c r="B134" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6863,7 +6875,7 @@
       <c r="B135" t="n">
         <v>81.7</v>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6907,7 +6919,7 @@
       <c r="B136" t="n">
         <v>41.3</v>
       </c>
-      <c r="C136" s="5" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>D - Weak / Low-Quality</t>
         </is>
@@ -6951,7 +6963,7 @@
       <c r="B137" t="n">
         <v>88</v>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -6995,7 +7007,7 @@
       <c r="B138" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C138" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7044,7 +7056,7 @@
       <c r="B139" t="n">
         <v>94</v>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7093,7 +7105,7 @@
       <c r="B140" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -7137,7 +7149,7 @@
       <c r="B141" t="n">
         <v>76.59999999999999</v>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -7186,7 +7198,7 @@
       <c r="B142" t="n">
         <v>88</v>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7230,7 +7242,7 @@
       <c r="B143" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7279,7 +7291,7 @@
       <c r="B144" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7328,7 +7340,7 @@
       <c r="B145" t="n">
         <v>88</v>
       </c>
-      <c r="C145" s="3" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7372,7 +7384,7 @@
       <c r="B146" t="n">
         <v>71.8</v>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -7416,7 +7428,7 @@
       <c r="B147" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C147" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7465,7 +7477,7 @@
       <c r="B148" t="n">
         <v>68</v>
       </c>
-      <c r="C148" s="2" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -7509,7 +7521,7 @@
       <c r="B149" t="n">
         <v>68.7</v>
       </c>
-      <c r="C149" s="2" t="inlineStr">
+      <c r="C149" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -7558,7 +7570,7 @@
       <c r="B150" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7607,7 +7619,7 @@
       <c r="B151" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="C151" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7656,7 +7668,7 @@
       <c r="B152" t="n">
         <v>90</v>
       </c>
-      <c r="C152" s="3" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7705,7 +7717,7 @@
       <c r="B153" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7754,7 +7766,7 @@
       <c r="B154" t="n">
         <v>67.8</v>
       </c>
-      <c r="C154" s="2" t="inlineStr">
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -7803,7 +7815,7 @@
       <c r="B155" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C155" s="3" t="inlineStr">
+      <c r="C155" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7852,7 +7864,7 @@
       <c r="B156" t="n">
         <v>63.7</v>
       </c>
-      <c r="C156" s="4" t="inlineStr">
+      <c r="C156" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -7901,7 +7913,7 @@
       <c r="B157" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7945,7 +7957,7 @@
       <c r="B158" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C158" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -7994,7 +8006,7 @@
       <c r="B159" t="n">
         <v>88</v>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C159" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8043,7 +8055,7 @@
       <c r="B160" t="n">
         <v>77.2</v>
       </c>
-      <c r="C160" s="2" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -8092,7 +8104,7 @@
       <c r="B161" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C161" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8141,7 +8153,7 @@
       <c r="B162" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C162" s="3" t="inlineStr">
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8190,7 +8202,7 @@
       <c r="B163" t="n">
         <v>95</v>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8239,7 +8251,7 @@
       <c r="B164" t="n">
         <v>87</v>
       </c>
-      <c r="C164" s="3" t="inlineStr">
+      <c r="C164" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8288,7 +8300,7 @@
       <c r="B165" t="n">
         <v>94</v>
       </c>
-      <c r="C165" s="3" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8337,7 +8349,7 @@
       <c r="B166" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C166" s="3" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8386,7 +8398,7 @@
       <c r="B167" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C167" s="3" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8435,7 +8447,7 @@
       <c r="B168" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="C168" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8484,7 +8496,7 @@
       <c r="B169" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8533,7 +8545,7 @@
       <c r="B170" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C170" s="3" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8582,7 +8594,7 @@
       <c r="B171" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C171" s="3" t="inlineStr">
+      <c r="C171" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8626,7 +8638,7 @@
       <c r="B172" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C172" s="3" t="inlineStr">
+      <c r="C172" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8675,7 +8687,7 @@
       <c r="B173" t="n">
         <v>88</v>
       </c>
-      <c r="C173" s="3" t="inlineStr">
+      <c r="C173" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8724,7 +8736,7 @@
       <c r="B174" t="n">
         <v>62.8</v>
       </c>
-      <c r="C174" s="4" t="inlineStr">
+      <c r="C174" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -8773,7 +8785,7 @@
       <c r="B175" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8817,7 +8829,7 @@
       <c r="B176" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C176" s="3" t="inlineStr">
+      <c r="C176" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8866,7 +8878,7 @@
       <c r="B177" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="C177" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8915,7 +8927,7 @@
       <c r="B178" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C178" s="3" t="inlineStr">
+      <c r="C178" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -8964,7 +8976,7 @@
       <c r="B179" t="n">
         <v>68.2</v>
       </c>
-      <c r="C179" s="2" t="inlineStr">
+      <c r="C179" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -9013,7 +9025,7 @@
       <c r="B180" t="n">
         <v>95</v>
       </c>
-      <c r="C180" s="3" t="inlineStr">
+      <c r="C180" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9062,7 +9074,7 @@
       <c r="B181" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C181" s="3" t="inlineStr">
+      <c r="C181" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9111,7 +9123,7 @@
       <c r="B182" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C182" s="3" t="inlineStr">
+      <c r="C182" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9160,7 +9172,7 @@
       <c r="B183" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="C183" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9209,7 +9221,7 @@
       <c r="B184" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9258,7 +9270,7 @@
       <c r="B185" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9307,7 +9319,7 @@
       <c r="B186" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C186" s="3" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9356,7 +9368,7 @@
       <c r="B187" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C187" s="3" t="inlineStr">
+      <c r="C187" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9400,7 +9412,7 @@
       <c r="B188" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="C188" s="3" t="inlineStr">
+      <c r="C188" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9444,7 +9456,7 @@
       <c r="B189" t="n">
         <v>49.8</v>
       </c>
-      <c r="C189" s="5" t="inlineStr">
+      <c r="C189" s="6" t="inlineStr">
         <is>
           <t>D - Weak / Low-Quality</t>
         </is>
@@ -9493,7 +9505,7 @@
       <c r="B190" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="C190" s="2" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -9542,7 +9554,7 @@
       <c r="B191" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C191" s="2" t="inlineStr">
+      <c r="C191" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -9591,7 +9603,7 @@
       <c r="B192" t="n">
         <v>88</v>
       </c>
-      <c r="C192" s="3" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9640,7 +9652,7 @@
       <c r="B193" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C193" s="3" t="inlineStr">
+      <c r="C193" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9689,7 +9701,7 @@
       <c r="B194" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C194" s="3" t="inlineStr">
+      <c r="C194" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9733,7 +9745,7 @@
       <c r="B195" t="n">
         <v>69.2</v>
       </c>
-      <c r="C195" s="2" t="inlineStr">
+      <c r="C195" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -9782,7 +9794,7 @@
       <c r="B196" t="n">
         <v>71.8</v>
       </c>
-      <c r="C196" s="2" t="inlineStr">
+      <c r="C196" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -9831,7 +9843,7 @@
       <c r="B197" t="n">
         <v>81.7</v>
       </c>
-      <c r="C197" s="3" t="inlineStr">
+      <c r="C197" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9880,7 +9892,7 @@
       <c r="B198" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C198" s="3" t="inlineStr">
+      <c r="C198" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9924,7 +9936,7 @@
       <c r="B199" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C199" s="3" t="inlineStr">
+      <c r="C199" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -9968,7 +9980,7 @@
       <c r="B200" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="C200" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10017,7 +10029,7 @@
       <c r="B201" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="C201" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10066,7 +10078,7 @@
       <c r="B202" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="C202" s="2" t="inlineStr">
+      <c r="C202" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -10115,7 +10127,7 @@
       <c r="B203" t="n">
         <v>41.3</v>
       </c>
-      <c r="C203" s="5" t="inlineStr">
+      <c r="C203" s="6" t="inlineStr">
         <is>
           <t>D - Weak / Low-Quality</t>
         </is>
@@ -10164,7 +10176,7 @@
       <c r="B204" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C204" s="3" t="inlineStr">
+      <c r="C204" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10213,7 +10225,7 @@
       <c r="B205" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C205" s="3" t="inlineStr">
+      <c r="C205" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10262,7 +10274,7 @@
       <c r="B206" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C206" s="3" t="inlineStr">
+      <c r="C206" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10306,7 +10318,7 @@
       <c r="B207" t="n">
         <v>53.8</v>
       </c>
-      <c r="C207" s="4" t="inlineStr">
+      <c r="C207" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -10355,7 +10367,7 @@
       <c r="B208" t="n">
         <v>81.7</v>
       </c>
-      <c r="C208" s="3" t="inlineStr">
+      <c r="C208" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10404,7 +10416,7 @@
       <c r="B209" t="n">
         <v>91</v>
       </c>
-      <c r="C209" s="3" t="inlineStr">
+      <c r="C209" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10453,7 +10465,7 @@
       <c r="B210" t="n">
         <v>77.7</v>
       </c>
-      <c r="C210" s="2" t="inlineStr">
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -10502,7 +10514,7 @@
       <c r="B211" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C211" s="3" t="inlineStr">
+      <c r="C211" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10551,7 +10563,7 @@
       <c r="B212" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C212" s="3" t="inlineStr">
+      <c r="C212" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10595,7 +10607,7 @@
       <c r="B213" t="n">
         <v>77.7</v>
       </c>
-      <c r="C213" s="2" t="inlineStr">
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -10644,7 +10656,7 @@
       <c r="B214" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C214" s="3" t="inlineStr">
+      <c r="C214" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10693,7 +10705,7 @@
       <c r="B215" t="n">
         <v>95</v>
       </c>
-      <c r="C215" s="3" t="inlineStr">
+      <c r="C215" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10742,7 +10754,7 @@
       <c r="B216" t="n">
         <v>81.7</v>
       </c>
-      <c r="C216" s="3" t="inlineStr">
+      <c r="C216" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10786,7 +10798,7 @@
       <c r="B217" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="C217" s="2" t="inlineStr">
+      <c r="C217" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -10830,7 +10842,7 @@
       <c r="B218" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C218" s="3" t="inlineStr">
+      <c r="C218" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10874,7 +10886,7 @@
       <c r="B219" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C219" s="3" t="inlineStr">
+      <c r="C219" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10923,7 +10935,7 @@
       <c r="B220" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C220" s="3" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -10972,7 +10984,7 @@
       <c r="B221" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C221" s="3" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11016,7 +11028,7 @@
       <c r="B222" t="n">
         <v>87</v>
       </c>
-      <c r="C222" s="3" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11065,7 +11077,7 @@
       <c r="B223" t="n">
         <v>91</v>
       </c>
-      <c r="C223" s="3" t="inlineStr">
+      <c r="C223" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11109,7 +11121,7 @@
       <c r="B224" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C224" s="3" t="inlineStr">
+      <c r="C224" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11153,7 +11165,7 @@
       <c r="B225" t="n">
         <v>74</v>
       </c>
-      <c r="C225" s="2" t="inlineStr">
+      <c r="C225" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -11202,7 +11214,7 @@
       <c r="B226" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C226" s="3" t="inlineStr">
+      <c r="C226" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11251,7 +11263,7 @@
       <c r="B227" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C227" s="3" t="inlineStr">
+      <c r="C227" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11300,7 +11312,7 @@
       <c r="B228" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C228" s="3" t="inlineStr">
+      <c r="C228" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11344,7 +11356,7 @@
       <c r="B229" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C229" s="3" t="inlineStr">
+      <c r="C229" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11393,7 +11405,7 @@
       <c r="B230" t="n">
         <v>76.2</v>
       </c>
-      <c r="C230" s="2" t="inlineStr">
+      <c r="C230" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -11437,7 +11449,7 @@
       <c r="B231" t="n">
         <v>71.8</v>
       </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="C231" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -11481,7 +11493,7 @@
       <c r="B232" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C232" s="2" t="inlineStr">
+      <c r="C232" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -11525,7 +11537,7 @@
       <c r="B233" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C233" s="3" t="inlineStr">
+      <c r="C233" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11569,7 +11581,7 @@
       <c r="B234" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C234" s="3" t="inlineStr">
+      <c r="C234" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11618,7 +11630,7 @@
       <c r="B235" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C235" s="3" t="inlineStr">
+      <c r="C235" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11667,7 +11679,7 @@
       <c r="B236" t="n">
         <v>72.8</v>
       </c>
-      <c r="C236" s="2" t="inlineStr">
+      <c r="C236" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -11716,7 +11728,7 @@
       <c r="B237" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C237" s="3" t="inlineStr">
+      <c r="C237" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11765,7 +11777,7 @@
       <c r="B238" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C238" s="3" t="inlineStr">
+      <c r="C238" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11814,7 +11826,7 @@
       <c r="B239" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C239" s="3" t="inlineStr">
+      <c r="C239" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11863,7 +11875,7 @@
       <c r="B240" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C240" s="3" t="inlineStr">
+      <c r="C240" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -11912,7 +11924,7 @@
       <c r="B241" t="n">
         <v>77.2</v>
       </c>
-      <c r="C241" s="2" t="inlineStr">
+      <c r="C241" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -11961,7 +11973,7 @@
       <c r="B242" t="n">
         <v>71.8</v>
       </c>
-      <c r="C242" s="2" t="inlineStr">
+      <c r="C242" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -12005,7 +12017,7 @@
       <c r="B243" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C243" s="3" t="inlineStr">
+      <c r="C243" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12054,7 +12066,7 @@
       <c r="B244" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C244" s="3" t="inlineStr">
+      <c r="C244" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12098,7 +12110,7 @@
       <c r="B245" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C245" s="3" t="inlineStr">
+      <c r="C245" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12147,7 +12159,7 @@
       <c r="B246" t="n">
         <v>72.8</v>
       </c>
-      <c r="C246" s="2" t="inlineStr">
+      <c r="C246" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -12196,7 +12208,7 @@
       <c r="B247" t="n">
         <v>88</v>
       </c>
-      <c r="C247" s="3" t="inlineStr">
+      <c r="C247" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12240,7 +12252,7 @@
       <c r="B248" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C248" s="3" t="inlineStr">
+      <c r="C248" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12284,7 +12296,7 @@
       <c r="B249" t="n">
         <v>88</v>
       </c>
-      <c r="C249" s="3" t="inlineStr">
+      <c r="C249" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12328,7 +12340,7 @@
       <c r="B250" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C250" s="2" t="inlineStr">
+      <c r="C250" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -12377,7 +12389,7 @@
       <c r="B251" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C251" s="3" t="inlineStr">
+      <c r="C251" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12421,7 +12433,7 @@
       <c r="B252" t="n">
         <v>95</v>
       </c>
-      <c r="C252" s="3" t="inlineStr">
+      <c r="C252" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12465,7 +12477,7 @@
       <c r="B253" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C253" s="3" t="inlineStr">
+      <c r="C253" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12514,7 +12526,7 @@
       <c r="B254" t="n">
         <v>88</v>
       </c>
-      <c r="C254" s="3" t="inlineStr">
+      <c r="C254" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12558,7 +12570,7 @@
       <c r="B255" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C255" s="3" t="inlineStr">
+      <c r="C255" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12607,7 +12619,7 @@
       <c r="B256" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C256" s="3" t="inlineStr">
+      <c r="C256" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12656,7 +12668,7 @@
       <c r="B257" t="n">
         <v>88</v>
       </c>
-      <c r="C257" s="3" t="inlineStr">
+      <c r="C257" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12700,7 +12712,7 @@
       <c r="B258" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C258" s="3" t="inlineStr">
+      <c r="C258" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12749,7 +12761,7 @@
       <c r="B259" t="n">
         <v>95</v>
       </c>
-      <c r="C259" s="3" t="inlineStr">
+      <c r="C259" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12798,7 +12810,7 @@
       <c r="B260" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="C260" s="2" t="inlineStr">
+      <c r="C260" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -12842,7 +12854,7 @@
       <c r="B261" t="n">
         <v>95</v>
       </c>
-      <c r="C261" s="3" t="inlineStr">
+      <c r="C261" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12886,7 +12898,7 @@
       <c r="B262" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C262" s="3" t="inlineStr">
+      <c r="C262" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12935,7 +12947,7 @@
       <c r="B263" t="n">
         <v>95</v>
       </c>
-      <c r="C263" s="3" t="inlineStr">
+      <c r="C263" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -12984,7 +12996,7 @@
       <c r="B264" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C264" s="3" t="inlineStr">
+      <c r="C264" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13028,7 +13040,7 @@
       <c r="B265" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C265" s="3" t="inlineStr">
+      <c r="C265" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13077,7 +13089,7 @@
       <c r="B266" t="n">
         <v>88</v>
       </c>
-      <c r="C266" s="3" t="inlineStr">
+      <c r="C266" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13121,7 +13133,7 @@
       <c r="B267" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C267" s="3" t="inlineStr">
+      <c r="C267" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13170,7 +13182,7 @@
       <c r="B268" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C268" s="3" t="inlineStr">
+      <c r="C268" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13214,7 +13226,7 @@
       <c r="B269" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C269" s="3" t="inlineStr">
+      <c r="C269" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13263,7 +13275,7 @@
       <c r="B270" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C270" s="3" t="inlineStr">
+      <c r="C270" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13312,7 +13324,7 @@
       <c r="B271" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="C271" s="3" t="inlineStr">
+      <c r="C271" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13361,7 +13373,7 @@
       <c r="B272" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C272" s="3" t="inlineStr">
+      <c r="C272" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13405,7 +13417,7 @@
       <c r="B273" t="n">
         <v>80.09999999999999</v>
       </c>
-      <c r="C273" s="3" t="inlineStr">
+      <c r="C273" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13454,7 +13466,7 @@
       <c r="B274" t="n">
         <v>95</v>
       </c>
-      <c r="C274" s="3" t="inlineStr">
+      <c r="C274" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13498,7 +13510,7 @@
       <c r="B275" t="n">
         <v>95</v>
       </c>
-      <c r="C275" s="3" t="inlineStr">
+      <c r="C275" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13547,7 +13559,7 @@
       <c r="B276" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C276" s="3" t="inlineStr">
+      <c r="C276" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13596,7 +13608,7 @@
       <c r="B277" t="n">
         <v>87</v>
       </c>
-      <c r="C277" s="3" t="inlineStr">
+      <c r="C277" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13645,7 +13657,7 @@
       <c r="B278" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C278" s="3" t="inlineStr">
+      <c r="C278" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13689,7 +13701,7 @@
       <c r="B279" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C279" s="3" t="inlineStr">
+      <c r="C279" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13738,7 +13750,7 @@
       <c r="B280" t="n">
         <v>87</v>
       </c>
-      <c r="C280" s="3" t="inlineStr">
+      <c r="C280" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13787,7 +13799,7 @@
       <c r="B281" t="n">
         <v>88</v>
       </c>
-      <c r="C281" s="3" t="inlineStr">
+      <c r="C281" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13831,7 +13843,7 @@
       <c r="B282" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="C282" s="3" t="inlineStr">
+      <c r="C282" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13880,7 +13892,7 @@
       <c r="B283" t="n">
         <v>81.59999999999999</v>
       </c>
-      <c r="C283" s="3" t="inlineStr">
+      <c r="C283" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13929,7 +13941,7 @@
       <c r="B284" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C284" s="3" t="inlineStr">
+      <c r="C284" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -13978,7 +13990,7 @@
       <c r="B285" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C285" s="3" t="inlineStr">
+      <c r="C285" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14022,7 +14034,7 @@
       <c r="B286" t="n">
         <v>77.2</v>
       </c>
-      <c r="C286" s="2" t="inlineStr">
+      <c r="C286" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14071,7 +14083,7 @@
       <c r="B287" t="n">
         <v>87</v>
       </c>
-      <c r="C287" s="3" t="inlineStr">
+      <c r="C287" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14120,7 +14132,7 @@
       <c r="B288" t="n">
         <v>77.2</v>
       </c>
-      <c r="C288" s="2" t="inlineStr">
+      <c r="C288" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14169,7 +14181,7 @@
       <c r="B289" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="C289" s="3" t="inlineStr">
+      <c r="C289" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14218,7 +14230,7 @@
       <c r="B290" t="n">
         <v>60.3</v>
       </c>
-      <c r="C290" s="4" t="inlineStr">
+      <c r="C290" s="5" t="inlineStr">
         <is>
           <t>C - Moderate / Watch</t>
         </is>
@@ -14267,7 +14279,7 @@
       <c r="B291" t="n">
         <v>86.59999999999999</v>
       </c>
-      <c r="C291" s="3" t="inlineStr">
+      <c r="C291" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14316,7 +14328,7 @@
       <c r="B292" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C292" s="3" t="inlineStr">
+      <c r="C292" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14365,7 +14377,7 @@
       <c r="B293" t="n">
         <v>68.8</v>
       </c>
-      <c r="C293" s="2" t="inlineStr">
+      <c r="C293" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14414,7 +14426,7 @@
       <c r="B294" t="n">
         <v>67.8</v>
       </c>
-      <c r="C294" s="2" t="inlineStr">
+      <c r="C294" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14458,7 +14470,7 @@
       <c r="B295" t="n">
         <v>71.8</v>
       </c>
-      <c r="C295" s="2" t="inlineStr">
+      <c r="C295" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14507,7 +14519,7 @@
       <c r="B296" t="n">
         <v>67.8</v>
       </c>
-      <c r="C296" s="2" t="inlineStr">
+      <c r="C296" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14551,7 +14563,7 @@
       <c r="B297" t="n">
         <v>77.7</v>
       </c>
-      <c r="C297" s="2" t="inlineStr">
+      <c r="C297" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14600,7 +14612,7 @@
       <c r="B298" t="n">
         <v>68.8</v>
       </c>
-      <c r="C298" s="2" t="inlineStr">
+      <c r="C298" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14649,7 +14661,7 @@
       <c r="B299" t="n">
         <v>95</v>
       </c>
-      <c r="C299" s="3" t="inlineStr">
+      <c r="C299" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14698,7 +14710,7 @@
       <c r="B300" t="n">
         <v>72.2</v>
       </c>
-      <c r="C300" s="2" t="inlineStr">
+      <c r="C300" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14747,7 +14759,7 @@
       <c r="B301" t="n">
         <v>77.2</v>
       </c>
-      <c r="C301" s="2" t="inlineStr">
+      <c r="C301" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14796,7 +14808,7 @@
       <c r="B302" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="C302" s="3" t="inlineStr">
+      <c r="C302" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14845,7 +14857,7 @@
       <c r="B303" t="n">
         <v>86.09999999999999</v>
       </c>
-      <c r="C303" s="3" t="inlineStr">
+      <c r="C303" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -14889,7 +14901,7 @@
       <c r="B304" t="n">
         <v>77.7</v>
       </c>
-      <c r="C304" s="2" t="inlineStr">
+      <c r="C304" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14938,7 +14950,7 @@
       <c r="B305" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C305" s="2" t="inlineStr">
+      <c r="C305" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
@@ -14987,7 +14999,7 @@
       <c r="B306" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="C306" s="3" t="inlineStr">
+      <c r="C306" s="4" t="inlineStr">
         <is>
           <t>A - High-Quality Setup</t>
         </is>
@@ -15036,7 +15048,7 @@
       <c r="B307" t="n">
         <v>78.09999999999999</v>
       </c>
-      <c r="C307" s="2" t="inlineStr">
+      <c r="C307" s="3" t="inlineStr">
         <is>
           <t>B - Good Setup</t>
         </is>
